--- a/data/books.xlsx
+++ b/data/books.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
   <si>
     <t>Date Completed</t>
   </si>
@@ -47,9 +47,6 @@
   </si>
   <si>
     <t>Loved the setting -Read this while moving and it ended up being a slog somehow. I love a drunken priest tho</t>
-  </si>
-  <si>
-    <t>Auguest 2026</t>
   </si>
   <si>
     <t>The Trial</t>
@@ -129,7 +126,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="mmmm yyyy"/>
+    <numFmt numFmtId="164" formatCode="M/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="m/d"/>
   </numFmts>
   <fonts count="6">
@@ -520,14 +517,14 @@
       <c r="Z2" s="2"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3">
+        <v>46235.0</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="D3" s="1">
         <v>231.0</v>
@@ -536,10 +533,10 @@
         <v>46117.0</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -566,10 +563,10 @@
         <v>46266.0</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" s="1">
         <v>161.0</v>
@@ -578,10 +575,10 @@
         <v>46117.0</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -608,10 +605,10 @@
         <v>46266.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1">
         <v>321.0</v>
@@ -620,10 +617,10 @@
         <v>9</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -650,22 +647,22 @@
         <v>46296.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" s="1">
         <v>283.0</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
@@ -689,13 +686,13 @@
     </row>
     <row r="7">
       <c r="A7" s="3">
-        <v>46296.0</v>
+        <v>46312.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7" s="1">
         <v>185.0</v>
@@ -704,10 +701,10 @@
         <v>46117.0</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -731,25 +728,25 @@
     </row>
     <row r="8">
       <c r="A8" s="3">
-        <v>46296.0</v>
+        <v>46312.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" s="1">
         <v>85.0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
